--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487720_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487720_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.501799999999999</v>
+        <v>10.2535</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7135</v>
+        <v>8.356199999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7883</v>
+        <v>1.8973</v>
       </c>
       <c r="G2" t="n">
         <v>4.668</v>
@@ -610,13 +610,13 @@
         <v>3.2985</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4248</v>
+        <v>1.1765</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2804</v>
+        <v>0.923</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1445</v>
+        <v>0.2535</v>
       </c>
       <c r="V2" t="n">
         <v>2.0806</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. COULIBALY</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4609</v>
+        <v>6.7796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7769</v>
+        <v>3.524</v>
       </c>
       <c r="F3" t="n">
-        <v>5.684</v>
+        <v>3.2556</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2457</v>
+        <v>3.5598</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9228</v>
+        <v>2.2368</v>
       </c>
       <c r="I3" t="n">
         <v>1.323</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1022</v>
+        <v>4.2581</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9804</v>
+        <v>3.3244</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1218</v>
+        <v>0.9337</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1435</v>
+        <v>-0.6983</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0577</v>
+        <v>-1.0875</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2012</v>
+        <v>0.3893</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5523</v>
+        <v>2.7164</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7164</v>
+        <v>3.6866</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6734</v>
+        <v>1.2004</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8389</v>
+        <v>0.8958</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8345</v>
+        <v>0.3045</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9896</v>
+        <v>-0.697</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9896</v>
+        <v>-0.0373</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>S. COULIBALY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3376</v>
+        <v>5.9091</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3819</v>
+        <v>0.4977</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9558</v>
+        <v>5.4115</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5598</v>
+        <v>2.2457</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2368</v>
+        <v>0.9228</v>
       </c>
       <c r="I4" t="n">
         <v>1.323</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2581</v>
+        <v>1.1022</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3244</v>
+        <v>0.9804</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9337</v>
+        <v>0.1218</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6983</v>
+        <v>1.1435</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0875</v>
+        <v>-0.0577</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3893</v>
+        <v>1.2012</v>
       </c>
       <c r="P4" t="n">
+        <v>1.5523</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.1642</v>
+      </c>
+      <c r="R4" t="n">
         <v>2.7164</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.9702</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3.6866</v>
-      </c>
       <c r="S4" t="n">
-        <v>0.7584</v>
+        <v>1.1216</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7537</v>
+        <v>0.5596</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0047</v>
+        <v>0.5619</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.697</v>
+        <v>0.9896</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0373</v>
+        <v>0.9896</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>L. SCHIEBELHUT LUIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.7288</v>
+        <v>4.5908</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8993</v>
+        <v>0.2222</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8295</v>
+        <v>4.3686</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2742</v>
+        <v>1.5623</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9756</v>
+        <v>0.1491</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2986</v>
+        <v>1.4132</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2155</v>
+        <v>1.1148</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5787</v>
+        <v>0.6303</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6368</v>
+        <v>0.4845</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0587</v>
+        <v>0.4475</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6031</v>
+        <v>-0.4812</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.9287</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3582</v>
+        <v>2.1344</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9105</v>
+        <v>-1.1642</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5523</v>
+        <v>3.2985</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4621</v>
+        <v>0.8942</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0883</v>
+        <v>0.2717</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3737</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6492</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. SCHIEBELHUT LUIS</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6233</v>
+        <v>2.9368</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7998</v>
+        <v>2.6796</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4231</v>
+        <v>0.2571</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5623</v>
+        <v>3.2742</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1491</v>
+        <v>1.9756</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4132</v>
+        <v>1.2986</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1148</v>
+        <v>3.2155</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6303</v>
+        <v>2.5787</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4845</v>
+        <v>0.6368</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4475</v>
+        <v>0.0587</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4812</v>
+        <v>-0.6031</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9287</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1344</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1642</v>
+        <v>-2.9105</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2985</v>
+        <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0733</v>
+        <v>1.67</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7504</v>
+        <v>0.8686</v>
       </c>
       <c r="U6" t="n">
-        <v>0.677</v>
+        <v>0.8014</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6492</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.1552</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5065</v>
+        <v>1.9129</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4016</v>
+        <v>0.0593</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9081</v>
+        <v>1.8536</v>
       </c>
       <c r="G7" t="n">
         <v>2.7345</v>
@@ -1000,13 +1000,13 @@
         <v>2.3284</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1698</v>
+        <v>0.2366</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3387</v>
+        <v>0.1222</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1689</v>
+        <v>0.1144</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2821</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. VAL GUTIERREZ</t>
+          <t>F. MORENO GUTIERREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2395</v>
+        <v>0.6764</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1193</v>
+        <v>-0.5454</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3588</v>
+        <v>1.2218</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.367</v>
+        <v>0.5604</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1351</v>
+        <v>-1.2959</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2319</v>
+        <v>1.8563</v>
       </c>
       <c r="J8" t="n">
-        <v>0.123</v>
+        <v>0.8065</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0824</v>
+        <v>-0.655</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0406</v>
+        <v>1.4615</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.49</v>
+        <v>-0.2462</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2175</v>
+        <v>-0.641</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2725</v>
+        <v>0.3948</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5821</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0244</v>
+        <v>0.1817</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0482</v>
+        <v>-0.0236</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0727</v>
+        <v>0.2053</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9045</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.2925</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. MORENO GUTIERREZ</t>
+          <t>D. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2154</v>
+        <v>0.5092</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0064</v>
+        <v>0.0414</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2218</v>
+        <v>0.4678</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5604</v>
+        <v>-0.367</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2959</v>
+        <v>-0.1351</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8563</v>
+        <v>-0.2319</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8065</v>
+        <v>0.123</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.655</v>
+        <v>0.0824</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4615</v>
+        <v>0.0406</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2462</v>
+        <v>-0.49</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.641</v>
+        <v>-0.2175</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3948</v>
+        <v>-0.2725</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9403</v>
+        <v>-0.194</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2793</v>
+        <v>0.2941</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4845</v>
+        <v>0.1124</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2053</v>
+        <v>0.1817</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9045</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.384</v>
+        <v>-0.3295</v>
       </c>
       <c r="E10" t="n">
         <v>-0.6873</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3033</v>
+        <v>0.3578</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3598</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0242</v>
+        <v>0.0303</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2501</v>
+        <v>-1.075</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2381</v>
+        <v>-2.4173</v>
       </c>
       <c r="F11" t="n">
-        <v>0.988</v>
+        <v>1.3423</v>
       </c>
       <c r="G11" t="n">
         <v>1.2021</v>
@@ -1312,13 +1312,13 @@
         <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1149</v>
+        <v>0.0603</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1469</v>
+        <v>-0.0323</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2618</v>
+        <v>0.0926</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9791</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5411</v>
+        <v>-3.8414</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4218</v>
+        <v>-1.7221</v>
       </c>
       <c r="F12" t="n">
         <v>-2.1194</v>
@@ -1390,10 +1390,10 @@
         <v>0.3881</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09760000000000001</v>
+        <v>-0.2027</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1951</v>
+        <v>-0.1052</v>
       </c>
       <c r="U12" t="n">
         <v>-0.09760000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6328</v>
+        <v>-5.3053</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.589</v>
+        <v>-4.2887</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0438</v>
+        <v>-1.0166</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1749</v>
@@ -1468,13 +1468,13 @@
         <v>0.7761</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5639</v>
+        <v>-0.2364</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4845</v>
+        <v>-0.1842</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0794</v>
+        <v>-0.0521</v>
       </c>
       <c r="V13" t="n">
         <v>-1.506</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.8058</v>
+        <v>23.0171</v>
       </c>
       <c r="E14" t="n">
-        <v>4.508299999999998</v>
+        <v>5.719599999999996</v>
       </c>
       <c r="F14" t="n">
-        <v>17.2975</v>
+        <v>17.2974</v>
       </c>
       <c r="G14" t="n">
         <v>15.2965</v>
       </c>
       <c r="H14" t="n">
-        <v>3.756900000000001</v>
+        <v>3.756899999999999</v>
       </c>
       <c r="I14" t="n">
         <v>11.5396</v>
@@ -1528,7 +1528,7 @@
         <v>5.589300000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6325999999999998</v>
+        <v>-0.6326000000000003</v>
       </c>
       <c r="N14" t="n">
         <v>-6.5829</v>
@@ -1546,13 +1546,13 @@
         <v>21.3435</v>
       </c>
       <c r="S14" t="n">
-        <v>5.215299999999999</v>
+        <v>6.4266</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1364</v>
+        <v>3.3474</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0788</v>
+        <v>3.078900000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-2.5864</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0799</v>
+        <v>3.1438</v>
       </c>
       <c r="E15" t="n">
-        <v>1.658</v>
+        <v>1.4578</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4219</v>
+        <v>1.686</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1524</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4677</v>
+        <v>-0.4038</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2412</v>
+        <v>-0.4414</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2265</v>
+        <v>0.0376</v>
       </c>
       <c r="V15" t="n">
         <v>2.7298</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8076</v>
+        <v>1.9265</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1256</v>
+        <v>3.2257</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3181</v>
+        <v>-1.2992</v>
       </c>
       <c r="G16" t="n">
         <v>0.0985</v>
@@ -1702,13 +1702,13 @@
         <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>0.339</v>
+        <v>0.4579</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3017</v>
+        <v>-0.2016</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6407</v>
+        <v>0.6595</v>
       </c>
       <c r="V16" t="n">
         <v>1.1761</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. VILA DE MIGUEL</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4014</v>
+        <v>0.2942</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1725</v>
+        <v>-0.4076</v>
       </c>
       <c r="F17" t="n">
-        <v>0.229</v>
+        <v>0.7018</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2927</v>
+        <v>1.6496</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7917</v>
+        <v>1.3882</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0844</v>
+        <v>0.2614</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9598</v>
+        <v>1.9567</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6271</v>
+        <v>1.9567</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6673</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2525</v>
+        <v>-0.3071</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8354</v>
+        <v>-0.5685</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4171</v>
+        <v>0.2614</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5821</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2178</v>
+        <v>-0.5793</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1828</v>
+        <v>-0.424</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4006</v>
+        <v>-0.1553</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>P. VILA DE MIGUEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1635</v>
+        <v>0.2435</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4076</v>
+        <v>-0.2279</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.4715</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6496</v>
+        <v>-0.2927</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3882</v>
+        <v>0.7917</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2614</v>
+        <v>-1.0844</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9567</v>
+        <v>0.9598</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9567</v>
+        <v>1.6271</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3071</v>
+        <v>-1.2525</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5685</v>
+        <v>-0.8354</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2614</v>
+        <v>-0.4171</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7099</v>
+        <v>-0.3757</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.424</v>
+        <v>-0.2176</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.286</v>
+        <v>-0.1581</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7318</v>
+        <v>-0.0462</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9048</v>
+        <v>-1.9876</v>
       </c>
       <c r="F19" t="n">
-        <v>0.173</v>
+        <v>1.9414</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2787</v>
+        <v>-1.4055</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1229</v>
+        <v>2.395</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1557</v>
+        <v>-3.8005</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.482</v>
+        <v>-0.6411</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.482</v>
+        <v>2.7311</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-3.3722</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7967</v>
+        <v>-0.7644</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.641</v>
+        <v>-0.3362</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1557</v>
+        <v>-0.4282</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1344</v>
+        <v>2.7164</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6065</v>
+        <v>-0.6214</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5473</v>
+        <v>-0.6107</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0592</v>
+        <v>-0.0106</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2239</v>
+        <v>0.2343</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2343</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4805</v>
+        <v>-1.1623</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5882</v>
+        <v>-1.3052</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1077</v>
+        <v>0.1429</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4055</v>
+        <v>-1.2787</v>
       </c>
       <c r="H20" t="n">
-        <v>2.395</v>
+        <v>-1.1229</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.8005</v>
+        <v>-0.1557</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6411</v>
+        <v>-0.482</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7311</v>
+        <v>-0.482</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.3722</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7644</v>
+        <v>-0.7967</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3362</v>
+        <v>-0.641</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4282</v>
+        <v>-0.1557</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7164</v>
+        <v>2.1344</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0556</v>
+        <v>0.1761</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2113</v>
+        <v>0.1469</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8443000000000001</v>
+        <v>0.0292</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2343</v>
+        <v>-1.2239</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2343</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5452</v>
+        <v>-1.2449</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6556</v>
+        <v>-1.3553</v>
       </c>
       <c r="F21" t="n">
         <v>0.1105</v>
@@ -2092,10 +2092,10 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2187</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1211</v>
+        <v>0.1792</v>
       </c>
       <c r="U21" t="n">
         <v>-0.09760000000000001</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7147</v>
+        <v>-3.5884</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5094</v>
+        <v>-2.8107</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2054</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3464</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2317</v>
+        <v>0.3581</v>
       </c>
       <c r="T22" t="n">
-        <v>1.458</v>
+        <v>0.1567</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2263</v>
+        <v>0.2014</v>
       </c>
       <c r="V22" t="n">
         <v>-0.0478</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0073</v>
+        <v>-4.2098</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7083</v>
+        <v>-4.2078</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2991</v>
+        <v>-0.0021</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6063</v>
@@ -2248,13 +2248,13 @@
         <v>1.9403</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0428</v>
+        <v>-0.2453</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9691</v>
+        <v>-0.4686</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0738</v>
+        <v>0.2232</v>
       </c>
       <c r="V23" t="n">
         <v>0.6119</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2301</v>
+        <v>-4.6572</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1661</v>
+        <v>-3.8658</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.064</v>
+        <v>-0.7914</v>
       </c>
       <c r="G24" t="n">
         <v>-4.224</v>
@@ -2326,13 +2326,13 @@
         <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0061</v>
+        <v>-0.4332</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8479</v>
+        <v>-0.5476</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1581</v>
+        <v>0.1144</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.5486</v>
+        <v>-9.835699999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.3135</v>
+        <v>-5.813</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.2351</v>
+        <v>-4.0227</v>
       </c>
       <c r="G25" t="n">
         <v>-3.218</v>
@@ -2404,13 +2404,13 @@
         <v>1.7463</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6738</v>
+        <v>-0.9609</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1508</v>
+        <v>-0.6503</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5231</v>
+        <v>-0.3107</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6119</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-21.8058</v>
+        <v>-19.1365</v>
       </c>
       <c r="E26" t="n">
         <v>-17.2974</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.5085</v>
+        <v>-1.839</v>
       </c>
       <c r="G26" t="n">
         <v>-15.2964</v>
@@ -2482,13 +2482,13 @@
         <v>17.4629</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.2152</v>
+        <v>-2.5459</v>
       </c>
       <c r="T26" t="n">
         <v>-3.079</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.1364</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>2.5865</v>
